--- a/extenbooks/S1008_extenbook.xlsx
+++ b/extenbooks/S1008_extenbook.xlsx
@@ -6251,7 +6251,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -7448,11 +7448,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7475,88 +7475,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Actual vs Warranted Stock Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ingested</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1008_research.json", "adequacy_report": "Technical/docs/chapters/CH10_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1008_DPR.md", "epr": "Technical/docs/series/S1008_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1008_load.py", "processor": "Technical/code/P02_processors/P02_S1008_construct.py", "validator": "Technical/code/V03_validators/V03_S1008_validate.py", "processed": "Technical/data/processed/S1008.parquet", "chopped_csv": "Technical/chopped/S1008.csv", "extenbook_xlsx": "Technical/extenbooks/S1008_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S1008-A", "S1008-B", "S1008-C"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["INTROPPRICE_preq", "INTROPPRICE_prstarshiller1", "eq_10.31_recursion"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1008_extenbook.xlsx
+++ b/extenbooks/S1008_extenbook.xlsx
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A151"/>
+  <dimension ref="A1:A161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6288,7 +6288,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>**S1008** is Shaikh's central empirical comparison in Chapter 10 (Figure 10.10):</t>
+          <t>**S1008** is Shaikh's central empirical comparison in Chapter 10 (Figure 10.13):</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.10, eq. (10.31), footnotes 24–25, p. 478</t>
+          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.13, eq. (10.31) p. 473, Appendix 10.1 p. 874</t>
         </is>
       </c>
     </row>
@@ -7055,6 +7055,68 @@
       <c r="A151" t="inlineStr">
         <is>
           <t>CD2 S059 used a growth-rate splice on warranted price for any extension — explicitly the No-Lazy-Splices-on-Derived-Quantities anti-pattern. CD3 reproduces eq. 10.31 directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>- **CD2 / CD3** — the predecessor builds of this dataset (earlier reconstructions; a "CD2 divergence" note reports how the earlier build differed, for information only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: Phase 5 is ingestion (building the book-period series); Phase 6 is extension (carrying the series forward with live data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>- **IROP / ROP** — incremental / average rate of profit (the return on newly added capital, or on the whole capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>- **FRED** — the Federal Reserve Bank of St. Louis public economic-data service (source of the modern extension inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>- **BEA / NIPA** — the U.S. Bureau of Economic Analysis and its National Income and Product Accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>- **No-Lazy-Splices rule** — an internal quality rule: a derived (formula) quantity is never extended by splicing onto the published rate; the formula is recomputed from extended components so it stays analytically consistent across the book/extension boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7495,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:26:13.956249+00:00</t>
+          <t>2026-07-02T06:18:31.610644+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1008_extenbook.xlsx
+++ b/extenbooks/S1008_extenbook.xlsx
@@ -6251,7 +6251,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:31.610644+00:00</t>
+          <t>2026-07-11T03:44:22.394601+00:00</t>
         </is>
       </c>
     </row>
@@ -7510,11 +7510,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7537,6 +7537,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INTROPPRICE_preq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Figure 10.13 (actual vs warranted stock price) via equation 10.31 forward iteration with pinned adj=6.75. Fixed multiple figure references (was 10.10, correct is 10.13; page 478 -&gt; 473/874).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1008_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1008_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>index_real_BEA_deflator</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
